--- a/data/event/event.xlsx
+++ b/data/event/event.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\event\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{946B8DC4-4324-492B-B600-8097A8CC2B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BFFD9DD-77E5-40D7-9BEB-540393C2C7B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="176">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -640,6 +640,48 @@
   </si>
   <si>
     <t>TVC:JP10Y</t>
+  </si>
+  <si>
+    <t>https://n.news.naver.com/mnews/article/002/0002442200?sid=102</t>
+  </si>
+  <si>
+    <t>ACOM0008</t>
+  </si>
+  <si>
+    <t>삼성전자 노사, 파업 하루 앞두고 극적 타결, 잠정 합의안 도출</t>
+  </si>
+  <si>
+    <t>KRX:005930, KRX:KOSPI</t>
+  </si>
+  <si>
+    <t>https://n.news.naver.com/mnews/article/001/0016090436?sid=101</t>
+  </si>
+  <si>
+    <t>AMKT0003</t>
+  </si>
+  <si>
+    <t>코스피 급반등에 매수 사이드카 발동</t>
+  </si>
+  <si>
+    <t>https://www.investing.com/news/earnings/nvidia-earnings-guidance-beat-expectations-stock-slips-after-hours-4702168</t>
+  </si>
+  <si>
+    <t>NASDAQ:NVDA</t>
+  </si>
+  <si>
+    <t>UTC-4</t>
+  </si>
+  <si>
+    <t>periodic</t>
+  </si>
+  <si>
+    <t>PCOM0001</t>
+  </si>
+  <si>
+    <t>ACOM0008, PCOM0001</t>
+  </si>
+  <si>
+    <t>엔비디아, 미국 장 마감 이후 1분기 실적발표. 매출액은 전년 대비 85% 급증한 816억1500만달러를 기록. 시장 전망치 788억6000만달러를 웃돌며 사상 최대치를 경신한 실적. 영업이익은 537억8300만달러를 기록해 전년 대비 147% 급증했으며 조정 주당순이익(EPS)은 1.87달러로 역시 시장 전망치 1.76달러를 상회</t>
   </si>
 </sst>
 </file>
@@ -1017,7 +1059,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12.5546875" style="10" bestFit="1" customWidth="1"/>
@@ -2287,6 +2329,126 @@
       </c>
       <c r="M33" s="1" t="s">
         <v>157</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34" s="10">
+        <v>46162</v>
+      </c>
+      <c r="B34" s="10">
+        <v>46162</v>
+      </c>
+      <c r="C34" s="3">
+        <v>0.9819444444444444</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" s="10">
+        <v>46163</v>
+      </c>
+      <c r="B35" s="10">
+        <v>46163</v>
+      </c>
+      <c r="C35" s="3">
+        <v>0.39166666666666666</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
+      <c r="A36" s="10">
+        <v>46162</v>
+      </c>
+      <c r="B36" s="10">
+        <v>46162</v>
+      </c>
+      <c r="C36" s="3">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/data/event/event.xlsx
+++ b/data/event/event.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\event\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BFFD9DD-77E5-40D7-9BEB-540393C2C7B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C18BCC2-D68D-4F8D-82AC-E0417D322528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="187">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -683,6 +683,39 @@
   <si>
     <t>엔비디아, 미국 장 마감 이후 1분기 실적발표. 매출액은 전년 대비 85% 급증한 816억1500만달러를 기록. 시장 전망치 788억6000만달러를 웃돌며 사상 최대치를 경신한 실적. 영업이익은 537억8300만달러를 기록해 전년 대비 147% 급증했으며 조정 주당순이익(EPS)은 1.87달러로 역시 시장 전망치 1.76달러를 상회</t>
   </si>
+  <si>
+    <t>https://n.news.naver.com/mnews/article/421/0008964837?sid=101</t>
+  </si>
+  <si>
+    <t>ACOM0009</t>
+  </si>
+  <si>
+    <t>삼성전자 노노 갈등 결국 법정으로…동행노조 "26일 투표 중지 가처분"</t>
+  </si>
+  <si>
+    <t>https://n.news.naver.com/mnews/article/055/0001357766?sid=101</t>
+  </si>
+  <si>
+    <t>ACOM0010</t>
+  </si>
+  <si>
+    <t>다음카카오, 5개 법인 파업 투표 가결</t>
+  </si>
+  <si>
+    <t>KRX:035720</t>
+  </si>
+  <si>
+    <t>AGEO0015</t>
+  </si>
+  <si>
+    <t>An Agreement has been largely negotiated, subject to finalization between the United States of America, the Islamic Republic of Iran, and the various other Countries…</t>
+  </si>
+  <si>
+    <t>United States, Iran</t>
+  </si>
+  <si>
+    <t>TVC:USOIL</t>
+  </si>
 </sst>
 </file>
 
@@ -692,7 +725,7 @@
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -734,6 +767,14 @@
       <name val="Verdana"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -755,30 +796,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1059,44 +1102,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M36"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="12.6"/>
+  <dimension ref="A1:M39"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="18.77734375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.77734375" style="1"/>
-    <col min="10" max="10" width="21.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.33203125" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.77734375" style="1"/>
+    <col min="1" max="1" width="12.5546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.21875" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5546875" style="12" customWidth="1"/>
+    <col min="8" max="8" width="18.77734375" style="12" customWidth="1"/>
+    <col min="9" max="9" width="8.77734375" style="12"/>
+    <col min="10" max="10" width="21.6640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.33203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.33203125" style="12" customWidth="1"/>
+    <col min="13" max="16384" width="8.77734375" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="8" customFormat="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="7" t="s">
         <v>38</v>
       </c>
       <c r="H1" s="8" t="s">
@@ -1119,1336 +1162,1450 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="10">
+      <c r="A2" s="9">
         <v>46154</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="9">
         <v>46154</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="10">
         <v>0.46527777777777779</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="12" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="10">
+      <c r="A3" s="9">
         <v>45629</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="9">
         <v>45629</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="10">
         <v>0.93541666666666667</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="M3" s="12" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="10">
+      <c r="A4" s="9">
         <v>45629</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="9">
         <v>45629</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="10">
         <v>0.98402777777777772</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="K4" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="L4" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="M4" s="12" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="10">
+      <c r="A5" s="9">
         <v>46156</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="9">
         <v>46156</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="10">
         <v>0.4513888888888889</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="M5" s="12" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="10">
+      <c r="A6" s="9">
         <v>46156</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="9">
         <v>46156</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="10">
         <v>0.49027777777777776</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="1" t="s">
+      <c r="M6" s="12" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="10">
+      <c r="A7" s="9">
         <v>46156</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="9">
         <v>46156</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="10">
         <v>0.99791666666666667</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="J7" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="K7" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="L7" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="M7" s="12" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="10">
+      <c r="A8" s="9">
         <v>44616</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="9">
         <v>44616</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="10">
         <v>0.24305555555555555</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="M8" s="12" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="10">
+      <c r="A9" s="9">
         <v>46156</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="9">
         <v>46156</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="10">
         <v>0.87847222222222221</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="J9" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="L9" s="12" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="10">
+      <c r="A10" s="9">
         <v>46155</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="9">
         <v>46157</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="10">
         <v>0.50555555555555554</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="H10" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="J10" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="M10" s="1" t="s">
+      <c r="M10" s="12" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:13">
-      <c r="A11" s="10">
+      <c r="A11" s="9">
         <v>46157</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="9">
         <v>46157</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="10">
         <v>0.50486111111111109</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="H11" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="I11" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J11" s="1" t="s">
+      <c r="I11" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="J11" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="K11" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="M11" s="1" t="s">
+      <c r="M11" s="12" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" s="10">
+      <c r="A12" s="9">
         <v>46157</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="9">
         <v>46157</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="10">
         <v>0.59375</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H12" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="I12" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="J12" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="M12" s="1" t="s">
+      <c r="M12" s="12" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" s="10">
+      <c r="A13" s="9">
         <v>46151</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="9">
         <v>46151</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="10">
         <v>0.48888888888888887</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="H13" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="I13" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J13" s="1" t="s">
+      <c r="I13" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="J13" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="M13" s="1" t="s">
+      <c r="M13" s="12" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="10">
+      <c r="A14" s="9">
         <v>46160</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="9">
         <v>46160</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="10">
         <v>0.49583333333333335</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="G14" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="I14" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="L14" s="1" t="s">
+      <c r="I14" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="L14" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="M14" s="1" t="s">
+      <c r="M14" s="12" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="10">
+      <c r="A15" s="9">
         <v>46157</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="9">
         <v>46157</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="10">
         <v>0.56111111111111112</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G15" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="H15" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="I15" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="L15" s="1" t="s">
+      <c r="I15" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="L15" s="12" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="10">
+      <c r="A16" s="9">
         <v>46160</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="9">
         <v>46160</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="10">
         <v>0.38819444444444445</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H16" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="I16" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K16" s="1" t="s">
+      <c r="I16" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="K16" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="L16" s="1" t="s">
+      <c r="L16" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="M16" s="1" t="s">
+      <c r="M16" s="12" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="10">
+      <c r="A17" s="9">
         <v>46160</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="9">
         <v>46160</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="10">
         <v>0.50694444444444442</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="H17" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="I17" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K17" s="1" t="s">
+      <c r="I17" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="J17" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="K17" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="L17" s="1" t="s">
+      <c r="L17" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="M17" s="1" t="s">
+      <c r="M17" s="12" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:13">
-      <c r="A18" s="10">
+      <c r="A18" s="9">
         <v>46160</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="9">
         <v>46160</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="10">
         <v>0.2673611111111111</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="H18" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="I18" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="M18" s="1" t="s">
+      <c r="I18" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="M18" s="12" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="19" spans="1:13">
-      <c r="A19" s="10">
+      <c r="A19" s="9">
         <v>46160</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="9">
         <v>46160</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="10">
         <v>0.21527777777777779</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G19" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="H19" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="I19" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="M19" s="1" t="s">
+      <c r="I19" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="M19" s="12" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" s="10">
+      <c r="A20" s="9">
         <v>46160</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="9">
         <v>46160</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="10">
         <v>0.56944444444444442</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E20" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="G20" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="H20" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="I20" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K20" s="1" t="s">
+      <c r="I20" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="J20" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="K20" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="L20" s="1" t="s">
+      <c r="L20" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="M20" s="1" t="s">
+      <c r="M20" s="12" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="10">
+      <c r="A21" s="9">
         <v>46160</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="9">
         <v>46160</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="10">
         <v>0.81666666666666665</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="G21" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="H21" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="I21" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="L21" s="1" t="s">
+      <c r="I21" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="L21" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="M21" s="1" t="s">
+      <c r="M21" s="12" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:13">
-      <c r="A22" s="10">
+      <c r="A22" s="9">
         <v>46161</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="9">
         <v>46161</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="10">
         <v>0.37986111111111109</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G22" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="H22" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="I22" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K22" s="1" t="s">
+      <c r="I22" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="K22" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="L22" s="1" t="s">
+      <c r="L22" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="M22" s="1" t="s">
+      <c r="M22" s="12" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:13">
-      <c r="A23" s="10">
+      <c r="A23" s="9">
         <v>46161</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="9">
         <v>46161</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="10">
         <v>0.30555555555555558</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G23" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="H23" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="I23" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J23" s="1" t="s">
+      <c r="I23" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="J23" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="K23" s="1" t="s">
+      <c r="K23" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="M23" s="1" t="s">
+      <c r="M23" s="12" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="24" spans="1:13">
-      <c r="A24" s="10">
+      <c r="A24" s="9">
         <v>46161</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="9">
         <v>46161</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="10">
         <v>0.41944444444444445</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="G24" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="H24" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="I24" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J24" s="1" t="s">
+      <c r="I24" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="J24" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="K24" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="L24" s="1" t="s">
+      <c r="L24" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="M24" s="1" t="s">
+      <c r="M24" s="12" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" s="10">
+      <c r="A25" s="9">
         <v>46161</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="9">
         <v>46161</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="10">
         <v>0.5083333333333333</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="G25" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="H25" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I25" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J25" s="1" t="s">
+      <c r="I25" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="J25" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="K25" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="M25" s="1" t="s">
+      <c r="M25" s="12" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="10">
+      <c r="A26" s="9">
         <v>46161</v>
       </c>
-      <c r="B26" s="10">
+      <c r="B26" s="9">
         <v>46161</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="10">
         <v>0.71458333333333335</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="G26" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="H26" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="I26" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J26" s="1" t="s">
+      <c r="I26" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="J26" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="K26" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="M26" s="1" t="s">
+      <c r="M26" s="12" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="27" spans="1:13">
-      <c r="A27" s="10">
+      <c r="A27" s="9">
         <v>46162</v>
       </c>
-      <c r="B27" s="10">
+      <c r="B27" s="9">
         <v>46162</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="10">
         <v>0.48055555555555557</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E27" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="G27" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="H27" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="I27" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K27" s="1" t="s">
+      <c r="I27" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="J27" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="K27" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="L27" s="1" t="s">
+      <c r="L27" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="M27" s="1" t="s">
+      <c r="M27" s="12" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="28" spans="1:13">
-      <c r="A28" s="10">
+      <c r="A28" s="9">
         <v>46162</v>
       </c>
-      <c r="B28" s="10">
+      <c r="B28" s="9">
         <v>46162</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="10">
         <v>0.48472222222222222</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="H28" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="I28" s="1" t="s">
+      <c r="I28" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="J28" s="1" t="s">
+      <c r="J28" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K28" s="1" t="s">
+      <c r="K28" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="M28" s="1" t="s">
+      <c r="M28" s="12" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="29" spans="1:13">
-      <c r="A29" s="10">
+      <c r="A29" s="9">
         <v>46162</v>
       </c>
-      <c r="B29" s="10">
+      <c r="B29" s="9">
         <v>46162</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29" s="10">
         <v>0.55833333333333335</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="G29" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="H29" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="I29" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K29" s="1" t="s">
+      <c r="I29" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="J29" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="K29" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="L29" s="1" t="s">
+      <c r="L29" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="M29" s="1" t="s">
+      <c r="M29" s="12" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="30" spans="1:13">
-      <c r="A30" s="10">
+      <c r="A30" s="9">
         <v>46162</v>
       </c>
-      <c r="B30" s="10">
+      <c r="B30" s="9">
         <v>46162</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="10">
         <v>0.61805555555555558</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="G30" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="H30" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="I30" s="1" t="s">
+      <c r="I30" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="J30" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K30" s="1" t="s">
+      <c r="J30" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="K30" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="M30" s="1" t="s">
+      <c r="M30" s="12" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="31" spans="1:13">
-      <c r="A31" s="10">
+      <c r="A31" s="9">
         <v>46162</v>
       </c>
-      <c r="B31" s="10">
+      <c r="B31" s="9">
         <v>46162</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="10">
         <v>0.65763888888888888</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E31" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="G31" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="H31" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="I31" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K31" s="1" t="s">
+      <c r="I31" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="J31" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="K31" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="L31" s="1" t="s">
+      <c r="L31" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="M31" s="1" t="s">
+      <c r="M31" s="12" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="32" spans="1:13">
-      <c r="A32" s="10">
+      <c r="A32" s="9">
         <v>46162</v>
       </c>
-      <c r="B32" s="10">
+      <c r="B32" s="9">
         <v>46162</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="10">
         <v>0.59166666666666667</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E32" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G32" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="H32" s="1" t="s">
+      <c r="H32" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="I32" s="1" t="s">
+      <c r="I32" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="J32" s="1" t="s">
+      <c r="J32" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="K32" s="1" t="s">
+      <c r="K32" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="M32" s="1" t="s">
+      <c r="M32" s="12" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="33" spans="1:13">
-      <c r="A33" s="10">
+      <c r="A33" s="9">
         <v>46161</v>
       </c>
-      <c r="B33" s="10">
+      <c r="B33" s="9">
         <v>46161</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C33" s="10">
         <v>0.45208333333333334</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="G33" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="H33" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="I33" s="1" t="s">
+      <c r="I33" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="J33" s="1" t="s">
+      <c r="J33" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="L33" s="1" t="s">
+      <c r="L33" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="M33" s="1" t="s">
+      <c r="M33" s="12" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="34" spans="1:13">
-      <c r="A34" s="10">
+      <c r="A34" s="9">
         <v>46162</v>
       </c>
-      <c r="B34" s="10">
+      <c r="B34" s="9">
         <v>46162</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34" s="10">
         <v>0.9819444444444444</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="G34" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="H34" s="1" t="s">
+      <c r="H34" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="I34" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K34" s="1" t="s">
+      <c r="I34" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="J34" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="K34" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="L34" s="1" t="s">
+      <c r="L34" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="M34" s="1" t="s">
+      <c r="M34" s="12" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="35" spans="1:13">
-      <c r="A35" s="10">
+      <c r="A35" s="9">
         <v>46163</v>
       </c>
-      <c r="B35" s="10">
+      <c r="B35" s="9">
         <v>46163</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="10">
         <v>0.39166666666666666</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E35" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F35" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="G35" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="H35" s="1" t="s">
+      <c r="H35" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="I35" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K35" s="1" t="s">
+      <c r="I35" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="J35" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="K35" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="L35" s="1" t="s">
+      <c r="L35" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="M35" s="1" t="s">
+      <c r="M35" s="12" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="36" spans="1:13">
-      <c r="A36" s="10">
+      <c r="A36" s="9">
         <v>46162</v>
       </c>
-      <c r="B36" s="10">
+      <c r="B36" s="9">
         <v>46162</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="10">
         <v>0.66666666666666663</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D36" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E36" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F36" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="G36" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="H36" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="I36" s="1" t="s">
+      <c r="I36" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="J36" s="1" t="s">
+      <c r="J36" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="L36" s="1" t="s">
+      <c r="L36" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="M36" s="1" t="s">
+      <c r="M36" s="12" t="s">
         <v>169</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
+      <c r="A37" s="9">
+        <v>46167</v>
+      </c>
+      <c r="B37" s="9">
+        <v>46167</v>
+      </c>
+      <c r="C37" s="10">
+        <v>0.72083333333333333</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="H37" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="I37" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="J37" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="K37" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="L37" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="M37" s="12" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
+      <c r="A38" s="9">
+        <v>46162</v>
+      </c>
+      <c r="B38" s="9">
+        <v>46162</v>
+      </c>
+      <c r="C38" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="G38" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="H38" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="I38" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="J38" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="L38" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="M38" s="12" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
+      <c r="A39" s="9">
+        <v>46165</v>
+      </c>
+      <c r="B39" s="9">
+        <v>46165</v>
+      </c>
+      <c r="C39" s="10">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G39" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="H39" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="I39" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="J39" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="L39" s="12" t="s">
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -2470,22 +2627,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="8"/>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
+      <c r="A1" s="4"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2499,7 +2656,7 @@
       <c r="C3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2513,7 +2670,7 @@
       <c r="C4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2527,7 +2684,7 @@
       <c r="C5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2541,7 +2698,7 @@
       <c r="C6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2555,7 +2712,7 @@
       <c r="C7" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="3" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2569,7 +2726,7 @@
       <c r="C8" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="2" t="s">
         <v>46</v>
       </c>
     </row>
